--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N80_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N80_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.7752065606074</v>
+        <v>1.913471066098702</v>
       </c>
       <c r="D2" t="n">
-        <v>18.44357897746099</v>
+        <v>2.997081583837411</v>
       </c>
       <c r="E2" t="n">
-        <v>5.348619924657229</v>
+        <v>0.8691507377568</v>
       </c>
       <c r="F2" t="n">
-        <v>4.840254975646893</v>
+        <v>0.7865414335426201</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.3114255904977</v>
+        <v>4.113106658455876</v>
       </c>
       <c r="D3" t="n">
-        <v>20.83960099125749</v>
+        <v>3.386435161079342</v>
       </c>
       <c r="E3" t="n">
-        <v>5.348619924657229</v>
+        <v>0.8691507377568</v>
       </c>
       <c r="F3" t="n">
-        <v>4.840254975646893</v>
+        <v>0.7865414335426201</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.43391532082797</v>
+        <v>3.320511239634545</v>
       </c>
       <c r="D4" t="n">
-        <v>23.38712233109386</v>
+        <v>3.800407378802753</v>
       </c>
       <c r="E4" t="n">
-        <v>5.348619924657229</v>
+        <v>0.8691507377568</v>
       </c>
       <c r="F4" t="n">
-        <v>4.840254975646893</v>
+        <v>0.7865414335426201</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.39314764288196</v>
+        <v>3.963886491968319</v>
       </c>
       <c r="D5" t="n">
-        <v>10.46646498814312</v>
+        <v>1.700800560573258</v>
       </c>
       <c r="E5" t="n">
-        <v>5.348619924657229</v>
+        <v>0.8691507377568</v>
       </c>
       <c r="F5" t="n">
-        <v>4.840254975646893</v>
+        <v>0.7865414335426201</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
